--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486348_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486348_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4105</v>
+        <v>3.7343</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8134</v>
+        <v>5.2605</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4029</v>
+        <v>-1.5262</v>
       </c>
       <c r="G2" t="n">
         <v>4.0203</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3922</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3014</v>
+        <v>-0.8544</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9092</v>
+        <v>0.7859</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8036</v>
+        <v>2.8528</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0036</v>
+        <v>3.9603</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2</v>
+        <v>-1.1075</v>
       </c>
       <c r="G3" t="n">
         <v>3.6494</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4983</v>
+        <v>-0.4491</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7619</v>
+        <v>-0.8051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2635</v>
+        <v>0.356</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2638</v>
+        <v>0.3762</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8577</v>
+        <v>1.933</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5939</v>
+        <v>-1.5568</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1232</v>
+        <v>3.549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4927</v>
+        <v>1.1832</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.616</v>
+        <v>2.3659</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1127</v>
+        <v>4.3388</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8577</v>
+        <v>1.3171</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7451</v>
+        <v>3.0217</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2359</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.365</v>
+        <v>-0.1339</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>-0.6558</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1696</v>
+        <v>-0.5426</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7451</v>
+        <v>-0.2307</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5755</v>
+        <v>-0.3118</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2576</v>
+        <v>0.255</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7528</v>
+        <v>2.0713</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4951</v>
+        <v>-1.8163</v>
       </c>
       <c r="G5" t="n">
-        <v>3.549</v>
+        <v>2.3456</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1832</v>
+        <v>0.8698</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3659</v>
+        <v>1.4758</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3388</v>
+        <v>3.2358</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3171</v>
+        <v>0.8061</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0217</v>
+        <v>2.4296</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.8902</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1339</v>
+        <v>0.0636</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6558</v>
+        <v>-0.9539</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6612</v>
+        <v>-0.8529</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-1.1644</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2502</v>
+        <v>0.3115</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.094</v>
+        <v>-0.0406</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0028</v>
+        <v>0.5224</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9088</v>
+        <v>-0.5631</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3456</v>
+        <v>-0.1232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8698</v>
+        <v>0.4927</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4758</v>
+        <v>-0.616</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2358</v>
+        <v>0.1127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8061</v>
+        <v>0.8577</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4296</v>
+        <v>-0.7451</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8902</v>
+        <v>-0.2359</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0636</v>
+        <v>-0.365</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9539</v>
+        <v>0.1291</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0139</v>
+        <v>-0.1349</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2329</v>
+        <v>0.4098</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2191</v>
+        <v>-0.5447</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3663</v>
+        <v>-0.7903</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2306</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5969</v>
+        <v>-1.3503</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7589</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>0.74</v>
+        <v>0.316</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8736</v>
+        <v>0.2031</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1336</v>
+        <v>0.113</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.918</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2019</v>
+        <v>-0.8729</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0449</v>
+        <v>-0.7869</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1368</v>
+        <v>0.2036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1817</v>
+        <v>-0.9905</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5756</v>
+        <v>0.5688</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0547</v>
+        <v>1.3504</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6303</v>
+        <v>-0.7817</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4694</v>
+        <v>-1.3556</v>
       </c>
       <c r="N8" t="n">
-        <v>0.082</v>
+        <v>-1.1468</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5514</v>
+        <v>-0.2088</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3288</v>
+        <v>-1.0914</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3425</v>
+        <v>-0.4867</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6713</v>
+        <v>-0.6048</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2228</v>
+        <v>-0.8395</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4353</v>
+        <v>-0.918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2125</v>
+        <v>0.0786</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3441</v>
+        <v>-1.0449</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1855</v>
+        <v>0.1368</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1586</v>
+        <v>-1.1817</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.5756</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0516</v>
+        <v>0.0547</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>-0.6303</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4073</v>
+        <v>-0.4694</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1339</v>
+        <v>0.082</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2733</v>
+        <v>-0.5514</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6612</v>
+        <v>0.2055</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.411</v>
+        <v>-0.3425</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2502</v>
+        <v>0.548</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2254</v>
+        <v>-1.1042</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3217</v>
+        <v>-1.2551</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.1509</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7869</v>
+        <v>-0.3441</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2036</v>
+        <v>-0.1855</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9905</v>
+        <v>-0.1586</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5688</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3504</v>
+        <v>-0.0516</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7817</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3556</v>
+        <v>-0.4073</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1468</v>
+        <v>-0.1339</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2088</v>
+        <v>-0.2733</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.526</v>
+        <v>-0.5426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8904</v>
+        <v>-0.2307</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.3118</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.687</v>
+        <v>-2.8412</v>
       </c>
       <c r="E11" t="n">
         <v>-0.5496</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1374</v>
+        <v>-2.2916</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3255</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1833</v>
+        <v>0.0291</v>
       </c>
       <c r="T11" t="n">
         <v>-0.5564</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7396</v>
+        <v>0.5855</v>
       </c>
       <c r="V11" t="n">
         <v>0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4122</v>
+        <v>-4.2696</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9785</v>
+        <v>-2.8667</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4337</v>
+        <v>-1.4029</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3756</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1511</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1971</v>
+        <v>0.3088</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1886</v>
+        <v>-0.1577</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8004</v>
+        <v>-3.4579</v>
       </c>
       <c r="E13" t="n">
-        <v>8.457800000000001</v>
+        <v>8.8002</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.258</v>
+        <v>-12.2581</v>
       </c>
       <c r="G13" t="n">
-        <v>5.805199999999999</v>
+        <v>5.805200000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0.1674</v>
       </c>
       <c r="I13" t="n">
-        <v>5.637899999999999</v>
+        <v>5.6379</v>
       </c>
       <c r="J13" t="n">
         <v>20.9273</v>
       </c>
       <c r="K13" t="n">
-        <v>7.985800000000001</v>
+        <v>7.985799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>12.941</v>
@@ -1465,16 +1465,16 @@
         <v>-11.9628</v>
       </c>
       <c r="R13" t="n">
-        <v>8.700000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.3226</v>
+        <v>-2.9803</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.0917</v>
+        <v>-3.7492</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7690000000000001</v>
+        <v>0.7691000000000003</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0202</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1333</v>
+        <v>5.5745</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2404</v>
+        <v>5.6816</v>
       </c>
       <c r="F14" t="n">
         <v>-0.1071</v>
@@ -1546,10 +1546,10 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9626</v>
+        <v>0.4038</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2692</v>
+        <v>-0.2896</v>
       </c>
       <c r="U14" t="n">
         <v>0.6934</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1852</v>
+        <v>4.8865</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6702</v>
+        <v>5.3408</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4851</v>
+        <v>-0.4542</v>
       </c>
       <c r="G15" t="n">
         <v>3.5687</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.209</v>
+        <v>0.4924</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2209</v>
+        <v>-0.5504</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0119</v>
+        <v>1.0428</v>
       </c>
       <c r="V15" t="n">
         <v>0.3904</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0736</v>
+        <v>1.4305</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0504</v>
+        <v>1.1671</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9767</v>
+        <v>0.2634</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.908</v>
+        <v>-1.7023</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3861</v>
+        <v>-0.6449</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2941</v>
+        <v>-1.0574</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1767</v>
+        <v>-0.9364</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9855</v>
+        <v>0.0365</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1912</v>
+        <v>-0.9729</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0847</v>
+        <v>-0.7659</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5994</v>
+        <v>-0.6814</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4854</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1116</v>
+        <v>0.5678</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8736</v>
+        <v>0.4086</v>
       </c>
       <c r="U16" t="n">
-        <v>1.238</v>
+        <v>0.1592</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.695</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8216</v>
+        <v>-0.1034</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4966</v>
+        <v>0.2157</v>
       </c>
       <c r="F17" t="n">
-        <v>0.325</v>
+        <v>-0.3191</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7023</v>
+        <v>-0.1257</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6449</v>
+        <v>-1.2835</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0574</v>
+        <v>1.1578</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9364</v>
+        <v>0.6267</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0365</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9729</v>
+        <v>1.2622</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7659</v>
+        <v>-0.7523</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6814</v>
+        <v>-0.6479</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1044</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0411</v>
+        <v>-0.4128</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.262</v>
+        <v>-0.411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2209</v>
+        <v>-0.0018</v>
       </c>
       <c r="V17" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3368</v>
+        <v>-0.1517</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8632</v>
+        <v>1.3798</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5263</v>
+        <v>-1.5315</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1948</v>
+        <v>-0.908</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9313</v>
+        <v>0.3861</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.126</v>
+        <v>-1.2941</v>
       </c>
       <c r="J18" t="n">
-        <v>1.921</v>
+        <v>1.1767</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6462</v>
+        <v>0.9855</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7251</v>
+        <v>0.1912</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1158</v>
+        <v>-2.0847</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7149</v>
+        <v>-0.5994</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4009</v>
+        <v>-1.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8992</v>
+        <v>0.8862</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9421</v>
+        <v>0.2031</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0429</v>
+        <v>0.6832</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8902</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8902</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1194</v>
+        <v>-0.2412</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3457</v>
+        <v>2.1926</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4652</v>
+        <v>-2.4339</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5631</v>
+        <v>-0.1948</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1915</v>
+        <v>1.9313</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7546</v>
+        <v>-2.126</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2516</v>
+        <v>1.921</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3719</v>
+        <v>2.6462</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8797</v>
+        <v>-0.7251</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8147</v>
+        <v>-2.1158</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1803</v>
+        <v>-0.7149</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6344</v>
+        <v>-1.4009</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1837</v>
+        <v>0.3212</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3567</v>
+        <v>0.2716</v>
       </c>
       <c r="U19" t="n">
-        <v>0.827</v>
+        <v>0.0496</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1651</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2157</v>
+        <v>0.8903</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3808</v>
+        <v>-1.4422</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1257</v>
+        <v>-0.3121</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2835</v>
+        <v>0.8274</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1578</v>
+        <v>-1.1395</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6267</v>
+        <v>2.2915</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.9257</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2622</v>
+        <v>0.3658</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7523</v>
+        <v>-2.6036</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6479</v>
+        <v>-1.0983</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1044</v>
+        <v>-1.5053</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4744</v>
+        <v>-0.1974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.411</v>
+        <v>-0.3136</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0635</v>
+        <v>0.1163</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2735</v>
+        <v>-1.1618</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6996</v>
+        <v>-1.5878</v>
       </c>
       <c r="F21" t="n">
         <v>0.4261</v>
@@ -2092,10 +2092,10 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0</v>
+        <v>0.1118</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U21" t="n">
         <v>0.3425</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7349</v>
+        <v>-1.2109</v>
       </c>
       <c r="E22" t="n">
-        <v>0.108</v>
+        <v>0.262</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8429</v>
+        <v>-1.4729</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3121</v>
+        <v>-2.7908</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8274</v>
+        <v>-1.2744</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1395</v>
+        <v>-1.5164</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2915</v>
+        <v>0.1394</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9257</v>
+        <v>0.0214</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3658</v>
+        <v>0.118</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6036</v>
+        <v>-2.9302</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0983</v>
+        <v>-1.2959</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5053</v>
+        <v>-1.6344</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3804</v>
+        <v>0.2749</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0959</v>
+        <v>0.1226</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2844</v>
+        <v>0.1523</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0356</v>
+        <v>-1.5954</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4086</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.627</v>
+        <v>-0.7117</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7908</v>
+        <v>-0.5631</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2744</v>
+        <v>0.1915</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5164</v>
+        <v>-0.7546</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1394</v>
+        <v>2.2516</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0214</v>
+        <v>1.3719</v>
       </c>
       <c r="L23" t="n">
-        <v>0.118</v>
+        <v>0.8797</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9302</v>
+        <v>-2.8147</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2959</v>
+        <v>-1.1803</v>
       </c>
       <c r="O23" t="n">
         <v>-1.6344</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5498</v>
+        <v>0.7078</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>0.1274</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0018</v>
+        <v>0.5804</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4216</v>
+        <v>-3.0748</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6239</v>
+        <v>-2.4004</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7977</v>
+        <v>-0.6744</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4594</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1798</v>
+        <v>0.167</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1507</v>
+        <v>0.274</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.800399999999999</v>
+        <v>3.800399999999998</v>
       </c>
       <c r="E25" t="n">
         <v>12.2581</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.457699999999999</v>
+        <v>-8.4575</v>
       </c>
       <c r="G25" t="n">
         <v>-5.805099999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1674000000000002</v>
+        <v>-0.1673999999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-5.637700000000001</v>
@@ -2389,7 +2389,7 @@
         <v>-20.9272</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.986000000000001</v>
+        <v>-7.986</v>
       </c>
       <c r="O25" t="n">
         <v>-12.9414</v>
@@ -2404,16 +2404,16 @@
         <v>11.9626</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3226</v>
+        <v>3.3227</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7692000000000003</v>
+        <v>-0.7688999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>4.0918</v>
+        <v>4.0919</v>
       </c>
       <c r="V25" t="n">
-        <v>3.020099999999999</v>
+        <v>3.0201</v>
       </c>
       <c r="W25" t="n">
         <v>6.6053</v>
